--- a/04_DESIGN_TABLES/DesignTable_6603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6603.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -961,24 +966,71 @@
           <t>6603-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>6603-06-06-06-FG</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9/16-18 (B (1) UN/UNF-2B) x 9/16-18 (B (2) UN/UNF-2B) x 9/16-18 (B (3) UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6603-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6603-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_6603-06-06-06-FG.stp, every value equal to the catalog within 0.005); end details from the end library: M5_1@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "M2 LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1: axis crossing to the swivel nut face; own STEP: nut faces 1.25 / 1.255 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); M10_1@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "M4 LGTH" = "0.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1: axis crossing to the swivel nose tip; own STEP: nose tips 0.865 / 0.87 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)) - catalog value kept; C3_1HEX@HEX: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 1 swivel nut hex; own STEP: nut A/F 0.688 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); M5_2@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "M2 LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2: axis crossing to the swivel nut face; own STEP: nut faces 1.25 / 1.255 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); M10_2@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "M4 LGTH" = "0.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2: axis crossing to the swivel nose tip; own STEP: nose tips 0.865 / 0.87 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)) - catalog value kept; C3_2HEX@HEX: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - run leg 2 swivel nut hex; own STEP: nut A/F 0.688 (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); M@DRIVE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "M LGTH" = "1.060" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - male JIC branch: axis crossing to the JIC tip; own STEP: branch tip at y 1.0601 (bbox, C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); Y@HEX: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: body flats 0.281 from the axis = 0.562 (tools/_out/wave2_shapes_20261008/PERLEGSW/evidence/step_survey.txt, this STEP); D1@BORE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "A1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - leg 1 bore; own STEP: bores 0.297 on all three legs (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); D2@BORE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "A2 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - leg 2 bore; own STEP: bores 0.297 on all three legs (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); D3@BORE: Brennan TFA catalog p.58 table TFA-p058-t01 "6603-FG FJS-FJS-MJ TEE" row 6603-06-06-06-FG col "A3 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 157.8, page verified True) [Brennan = yes 2026-10-18] - leg 3 bore; own STEP: bores 0.297 on all three legs (C_ownstep/measure/6603-06-06-06-FG.txt (swiv._measure_leg Brennan mode, bbox)); THDMAJ_B1@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B2@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B3@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6603-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6603-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 6603-6-6-6 (plain): M5 1.25 M10 0.88 M 1.08 C3 0.69 Y 0.63 D 0.30 (M / Y differ: forged 1.06 / 0.562)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -989,6 +1041,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>6603-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
